--- a/GameData/DataTables/Machines/MachineDefinitions.xlsx
+++ b/GameData/DataTables/Machines/MachineDefinitions.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <si>
     <t>#</t>
   </si>
@@ -74,6 +74,12 @@
     <t>Prefab</t>
   </si>
   <si>
+    <t>FootprintX</t>
+  </si>
+  <si>
+    <t>FootprintZ</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -89,6 +95,12 @@
     <t>Stable row identifier</t>
   </si>
   <si>
+    <t>交互占地沿本地X（米）。轴名写死是因为设计文档按「长×宽」记占地（见DEC-147与灰盒规格：轮式载体交互占地2.6×1.8米＝Z2.6×X1.8），不写死轴向会在实现侧再次推错</t>
+  </si>
+  <si>
+    <t>交互占地沿本地Z（米）。0表示该型号尚未配置占地，放置流程须以「未配置占地」拒绝而不是猜一个值</t>
+  </si>
+  <si>
     <t>10011</t>
   </si>
   <si>
@@ -126,6 +138,12 @@
   </si>
   <si>
     <t>Machines/WheeledCarrier</t>
+  </si>
+  <si>
+    <t>1.8</t>
+  </si>
+  <si>
+    <t>2.6</t>
   </si>
   <si>
     <t>10012</t>
@@ -219,7 +237,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:S8"/>
+  <dimension ref="A1:U8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -280,6 +298,12 @@
       <c r="S1" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="T1" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="U1" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
@@ -339,64 +363,76 @@
       <c r="S2" s="0" t="s">
         <v>19</v>
       </c>
+      <c r="T2" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="U2" s="0" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C3" s="0" t="s">
         <v>2</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F3" s="0" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I3" s="0" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J3" s="0" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K3" s="0" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L3" s="0" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M3" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="N3" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="O3" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="P3" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q3" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="R3" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="N3" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="O3" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="P3" s="0" t="s">
+      <c r="S3" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="Q3" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="R3" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="S3" s="0" t="s">
-        <v>21</v>
+      <c r="T3" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="U3" s="0" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="4">
@@ -404,7 +440,7 @@
         <v>0</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C4" s="0" t="s">
         <v>2</v>
@@ -456,6 +492,12 @@
       </c>
       <c r="S4" s="0" t="s">
         <v>19</v>
+      </c>
+      <c r="T4" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="U4" s="0" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="5">
@@ -463,58 +505,64 @@
         <v>2</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C5" s="0" t="s">
         <v>2</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F5" s="0" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I5" s="0" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J5" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="K5" s="0" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="L5" s="0" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M5" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="N5" s="0" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="O5" s="0" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="P5" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="Q5" s="0" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="R5" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="S5" s="0" t="s">
-        <v>37</v>
+        <v>41</v>
+      </c>
+      <c r="T5" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="U5" s="0" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="6">
@@ -522,58 +570,64 @@
         <v>2</v>
       </c>
       <c r="B6" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="H6" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="J6" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="K6" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="L6" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="M6" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="N6" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="O6" s="0" t="s">
         <v>38</v>
       </c>
-      <c r="C6" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="G6" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="H6" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="I6" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="J6" s="0" t="s">
+      <c r="P6" s="0" t="s">
         <v>39</v>
       </c>
-      <c r="K6" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="L6" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="M6" s="0" t="s">
+      <c r="Q6" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="R6" s="0" t="s">
         <v>40</v>
       </c>
-      <c r="N6" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="O6" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="P6" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q6" s="0" t="s">
+      <c r="S6" s="0" t="s">
         <v>41</v>
       </c>
-      <c r="R6" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="S6" s="0" t="s">
-        <v>37</v>
+      <c r="T6" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="U6" s="0" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="7">
@@ -581,58 +635,64 @@
         <v>2</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C7" s="0" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="F7" s="0" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G7" s="0" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H7" s="0" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I7" s="0" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J7" s="0" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="K7" s="0" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="L7" s="0" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M7" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="N7" s="0" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="O7" s="0" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="P7" s="0" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="Q7" s="0" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="R7" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="S7" s="0" t="s">
-        <v>50</v>
+        <v>56</v>
+      </c>
+      <c r="T7" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="U7" s="0" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="8">
@@ -640,58 +700,64 @@
         <v>2</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="C8" s="0" t="s">
         <v>2</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="F8" s="0" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G8" s="0" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H8" s="0" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I8" s="0" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J8" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="K8" s="0" t="s">
         <v>52</v>
       </c>
-      <c r="K8" s="0" t="s">
+      <c r="L8" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="M8" s="0" t="s">
         <v>46</v>
       </c>
-      <c r="L8" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="M8" s="0" t="s">
+      <c r="N8" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="O8" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="P8" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q8" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="R8" s="0" t="s">
         <v>40</v>
       </c>
-      <c r="N8" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="O8" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="P8" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q8" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="R8" s="0" t="s">
-        <v>36</v>
-      </c>
       <c r="S8" s="0" t="s">
-        <v>50</v>
+        <v>56</v>
+      </c>
+      <c r="T8" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="U8" s="0" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
